--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260703.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>93,804,000</t>
+          <t>3,319,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,319,000</t>
+          <t>93,804,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2,114,000</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>2,114,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
